--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2123</v>
+        <v>2136</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,11 +644,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7161</v>
+        <v>7203</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2123</v>
+        <v>2136</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7161</v>
+        <v>7203</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2136</v>
+        <v>2152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1516</v>
+        <v>1541</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7203</v>
+        <v>7254</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2136</v>
+        <v>2152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1516</v>
+        <v>1541</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7203</v>
+        <v>7254</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2152</v>
+        <v>2186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1541</v>
+        <v>1566</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7254</v>
+        <v>7336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2152</v>
+        <v>2186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1541</v>
+        <v>1566</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7254</v>
+        <v>7336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -506,22 +501,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2186</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>2249</v>
+      </c>
+      <c r="G2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79764</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79764</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/l0hSA2KL1702521429527.jpeg</t>
         </is>
@@ -552,22 +542,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>624</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>641</v>
+      </c>
+      <c r="G3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78089</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78089</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/QqiJ6HfK1702365336991.jpeg</t>
         </is>
@@ -598,22 +583,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1566</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
+        <v>1654</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
         </is>
@@ -644,22 +624,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7336</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>7648</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
         </is>
@@ -690,22 +665,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>179</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>180</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
@@ -736,22 +706,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>178</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>212</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
         </is>
@@ -768,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,15 +772,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -832,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,15 +831,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -896,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,15 +890,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -974,22 +924,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2186</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>2249</v>
+      </c>
+      <c r="G2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79764</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79764</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/l0hSA2KL1702521429527.jpeg</t>
         </is>
@@ -1020,22 +965,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>624</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>641</v>
+      </c>
+      <c r="G3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78089</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78089</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/QqiJ6HfK1702365336991.jpeg</t>
         </is>
@@ -1066,22 +1006,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1566</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
+        <v>1654</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
         </is>
@@ -1112,22 +1047,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7336</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>7648</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
         </is>
@@ -1158,22 +1088,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>179</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>180</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
@@ -1204,22 +1129,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>178</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>212</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
         </is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,12 +482,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南宁·AP动漫游戏嘉年华</t>
+          <t>南宁·桂南动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -497,23 +497,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.28 17:00</t>
+          <t>2024.02.01 10:00-02.02 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2249</v>
+        <v>1688</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/l0hSA2KL1702521429527.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·第一届异次元动漫嘉年华</t>
+          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>临江路1号 邕江宾馆</t>
+          <t>民族大道106号 南宁国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.28 18:00</t>
+          <t>2024.02.15 09:30-02.16 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>641</v>
+        <v>7794</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/QqiJ6HfK1702365336991.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·桂南动漫游戏嘉年华</t>
+          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -579,23 +579,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1654</v>
+        <v>181</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,118 +605,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>民族大道106号 南宁国际会展中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.15 09:30-02.16 17:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7648</v>
+        <v>233</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-03-09</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>亭洪路45号 百益上河城</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>180</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>南宁·草莓动漫节</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>亭洪路45号 百益上河城</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
         </is>
@@ -851,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,12 +823,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南宁·AP动漫游戏嘉年华</t>
+          <t>南宁·桂南动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -920,23 +838,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.28 17:00</t>
+          <t>2024.02.01 10:00-02.02 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2249</v>
+        <v>1688</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/l0hSA2KL1702521429527.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
         </is>
       </c>
     </row>
@@ -946,38 +864,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·第一届异次元动漫嘉年华</t>
+          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>临江路1号 邕江宾馆</t>
+          <t>民族大道106号 南宁国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.28 18:00</t>
+          <t>2024.02.15 09:30-02.16 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>641</v>
+        <v>7794</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/QqiJ6HfK1702365336991.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
         </is>
       </c>
     </row>
@@ -987,12 +905,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·桂南动漫游戏嘉年华</t>
+          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1002,23 +920,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1654</v>
+        <v>181</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
       </c>
     </row>
@@ -1028,118 +946,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>民族大道106号 南宁国际会展中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.15 09:30-02.16 17:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7648</v>
+        <v>233</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-03-09</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>亭洪路45号 百益上河城</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>180</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>南宁·草莓动漫节</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>亭洪路45号 百益上河城</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
         </is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1688</v>
+        <v>1703</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7794</v>
+        <v>7855</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1688</v>
+        <v>1703</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7794</v>
+        <v>7855</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1703</v>
+        <v>1724</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7855</v>
+        <v>7916</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1703</v>
+        <v>1724</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7855</v>
+        <v>7916</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1724</v>
+        <v>1735</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7916</v>
+        <v>7966</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1724</v>
+        <v>1735</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7916</v>
+        <v>7966</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1735</v>
+        <v>1763</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7966</v>
+        <v>8057</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1735</v>
+        <v>1763</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7966</v>
+        <v>8057</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1763</v>
+        <v>1774</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8057</v>
+        <v>8101</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1763</v>
+        <v>1774</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8057</v>
+        <v>8101</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1774</v>
+        <v>1801</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8101</v>
+        <v>8172</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1774</v>
+        <v>1801</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8101</v>
+        <v>8172</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1801</v>
+        <v>1816</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8172</v>
+        <v>8214</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1801</v>
+        <v>1816</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8172</v>
+        <v>8214</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1816</v>
+        <v>1828</v>
       </c>
       <c r="G2" t="n">
         <v>70</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8214</v>
+        <v>8309</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1816</v>
+        <v>1828</v>
       </c>
       <c r="G2" t="n">
         <v>70</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8214</v>
+        <v>8309</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="G2" t="n">
         <v>70</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8309</v>
+        <v>8365</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="G2" t="n">
         <v>70</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8309</v>
+        <v>8365</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南宁·桂南动漫游戏嘉年华</t>
+          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>民族大道106号 南宁国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.02 17:00</t>
+          <t>2024.02.15 09:30-02.16 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1832</v>
+        <v>8447</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
+          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>民族大道106号 南宁国际会展中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.15 09:30-02.16 17:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8365</v>
+        <v>192</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -579,23 +579,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>191</v>
+        <v>365</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·草莓动漫节</t>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -620,23 +620,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.30 09:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>353</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>
       </c>
     </row>
@@ -823,38 +823,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南宁·桂南动漫游戏嘉年华</t>
+          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>民族大道106号 南宁国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.02 17:00</t>
+          <t>2024.02.15 09:30-02.16 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1832</v>
+        <v>8447</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79354</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/CIlf3jyZ1701747640038.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
         </is>
       </c>
     </row>
@@ -864,38 +864,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
+          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>民族大道106号 南宁国际会展中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.15 09:30-02.16 17:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8365</v>
+        <v>192</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -920,23 +920,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>191</v>
+        <v>365</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·草莓动漫节</t>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -961,23 +961,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.30 09:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>353</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>
       </c>
     </row>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8447</v>
+        <v>8524</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8447</v>
+        <v>8524</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8524</v>
+        <v>8612</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8524</v>
+        <v>8612</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8612</v>
+        <v>8674</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8612</v>
+        <v>8674</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8674</v>
+        <v>8762</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8674</v>
+        <v>8762</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8762</v>
+        <v>8810</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>342</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8762</v>
+        <v>8810</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>342</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8810</v>
+        <v>8893</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -595,7 +595,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FSJIeLNT1707130460798.jpeg</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>342</v>
+        <v>448</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8810</v>
+        <v>8893</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -936,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/DTcCPBbg1705477910107.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FSJIeLNT1707130460798.jpeg</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>342</v>
+        <v>448</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8893</v>
+        <v>8951</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8893</v>
+        <v>8951</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8951</v>
+        <v>9050</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +696,47 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>南宁·卡农·世界经典音乐之旅音乐会</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>龙堤路25号 南宁文化艺术中心</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024.03.30 20:00-03.30 21:30</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81798</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/Tv5lqcVn1707214065277.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8951</v>
+        <v>9050</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -883,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -951,31 +992,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
+          <t>南宁·卡农·世界经典音乐之旅音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>龙堤路25号 南宁文化艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.30 09:00-03.31 17:30</t>
+          <t>2024.03.30 20:00-03.30 21:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81798</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/Tv5lqcVn1707214065277.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>亭洪路45号 百益上河城</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024.03.30 09:00-03.31 17:30</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>452</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9050</v>
+        <v>9100</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9050</v>
+        <v>9100</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9100</v>
+        <v>9176</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -595,7 +595,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FSJIeLNT1707130460798.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9100</v>
+        <v>9176</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FSJIeLNT1707130460798.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9176</v>
+        <v>9227</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9176</v>
+        <v>9227</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9227</v>
+        <v>9300</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·草莓动漫节</t>
+          <t>南宁·0316全职only-全明星周末</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>大学东路158号 维也纳国际酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:30-03.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>487</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81834</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5RPyTNNO1707363370492.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -620,21 +620,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.30 09:00-03.31 17:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>457</v>
+        <v>500</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>亭洪路45号 百益上河城</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024.03.30 09:00-03.31 17:30</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>458</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>
@@ -810,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9227</v>
+        <v>9300</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -924,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -951,33 +992,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·草莓动漫节</t>
+          <t>南宁·0316全职only-全明星周末</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>大学东路158号 维也纳国际酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:30-03.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>487</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81834</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5RPyTNNO1707363370492.jpeg</t>
         </is>
       </c>
     </row>
@@ -987,38 +1028,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·卡农·世界经典音乐之旅音乐会</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>龙堤路25号 南宁文化艺术中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.30 20:00-03.30 21:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81798</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/Tv5lqcVn1707214065277.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
         </is>
       </c>
     </row>
@@ -1033,31 +1074,72 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
+          <t>南宁·卡农·世界经典音乐之旅音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>龙堤路25号 南宁文化艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.30 09:00-03.31 17:30</t>
+          <t>2024.03.30 20:00-03.30 21:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81798</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/Tv5lqcVn1707214065277.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>亭洪路45号 百益上河城</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024.03.30 09:00-03.31 17:30</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>458</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9300</v>
+        <v>9334</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9300</v>
+        <v>9334</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9334</v>
+        <v>9396</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9334</v>
+        <v>9396</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9396</v>
+        <v>9441</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9396</v>
+        <v>9441</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9441</v>
+        <v>9559</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9441</v>
+        <v>9559</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9559</v>
+        <v>9627</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9559</v>
+        <v>9627</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9627</v>
+        <v>9739</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9627</v>
+        <v>9739</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9739</v>
+        <v>9802</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9739</v>
+        <v>9802</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9802</v>
+        <v>9905</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9802</v>
+        <v>9905</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9905</v>
+        <v>9969</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9905</v>
+        <v>9969</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9969</v>
+        <v>10093</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9969</v>
+        <v>10093</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10093</v>
+        <v>10178</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10093</v>
+        <v>10178</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10178</v>
+        <v>10419</v>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -564,7 +564,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -605,7 +605,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -646,7 +646,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -746,7 +746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10178</v>
+        <v>10419</v>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10419</v>
+        <v>10596</v>
       </c>
       <c r="G2" t="n">
         <v>62</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10419</v>
+        <v>10596</v>
       </c>
       <c r="G2" t="n">
         <v>62</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10596</v>
+        <v>10750</v>
       </c>
       <c r="G2" t="n">
         <v>62</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>671</v>
+        <v>712</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10596</v>
+        <v>10750</v>
       </c>
       <c r="G2" t="n">
         <v>62</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>671</v>
+        <v>712</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10750</v>
+        <v>10871</v>
       </c>
       <c r="G2" t="n">
         <v>62</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10750</v>
+        <v>10871</v>
       </c>
       <c r="G2" t="n">
         <v>62</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
+          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>民族大道106号 南宁国际会展中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.15 09:30-02.16 17:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10871</v>
+        <v>246</v>
       </c>
       <c r="G2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
+          <t>南宁·0316全职only-全明星周末</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>大学东路158号 维也纳国际酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 10:30-03.16 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81834</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5RPyTNNO1707363370492.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·0316全职only-全明星周末</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大学东路158号 维也纳国际酒店</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 10:30-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>795</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81834</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5RPyTNNO1707363370492.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·草莓动漫节</t>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -620,62 +620,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.30 09:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>740</v>
+        <v>516</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>亭洪路45号 百益上河城</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024.03.30 09:00-03.31 17:30</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>503</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>
@@ -851,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,38 +864,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南宁·2024良牙动漫冬季盛典（冬典）</t>
+          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>民族大道106号 南宁国际会展中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.15 09:30-02.16 17:30</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10871</v>
+        <v>246</v>
       </c>
       <c r="G2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/YriBERx81701329557375.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
         </is>
       </c>
     </row>
@@ -946,38 +905,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·第五届小蜜蜂动漫嘉年华</t>
+          <t>南宁·0316全职only-全明星周末</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>大学东路158号 维也纳国际酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 10:30-03.16 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79051</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81834</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bv8DJewO1701071702232.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5RPyTNNO1707363370492.jpeg</t>
         </is>
       </c>
     </row>
@@ -992,33 +951,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南宁·0316全职only-全明星周末</t>
+          <t>南宁·草莓动漫节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大学东路158号 维也纳国际酒店</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 10:30-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>795</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81834</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5RPyTNNO1707363370492.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
         </is>
       </c>
     </row>
@@ -1028,38 +987,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南宁·草莓动漫节</t>
+          <t>南宁·卡农·世界经典音乐之旅音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>亭洪路45号 百益上河城</t>
+          <t>龙堤路25号 南宁文化艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.30 20:00-03.30 21:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>740</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80943</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81798</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/vF9kexbx1707289709364.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/Tv5lqcVn1707214065277.jpeg</t>
         </is>
       </c>
     </row>
@@ -1074,72 +1033,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南宁·卡农·世界经典音乐之旅音乐会</t>
+          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>龙堤路25号 南宁文化艺术中心</t>
+          <t>亭洪路45号 百益上河城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.30 20:00-03.30 21:30</t>
+          <t>2024.03.30 09:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>516</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81798</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/Tv5lqcVn1707214065277.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>南宁·第一届ANE·DACG动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>亭洪路45号 百益上河城</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2024.03.30 09:00-03.31 17:30</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>503</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81658</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
         </is>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>830</v>
+        <v>876</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>830</v>
+        <v>876</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>876</v>
+        <v>913</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>876</v>
+        <v>913</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>913</v>
+        <v>964</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>913</v>
+        <v>964</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>995</v>
+        <v>1031</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>995</v>
+        <v>1031</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -528,7 +528,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·0316全职only-全明星周末</t>
+          <t>南宁·0316全职only-全明星周末（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -542,10 +542,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>95</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -883,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -910,7 +912,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南宁·0316全职only-全明星周末</t>
+          <t>南宁·0316全职only-全明星周末（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -924,10 +926,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>95</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -965,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1047,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1145</v>
+        <v>1163</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1145</v>
+        <v>1163</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1190</v>
+        <v>1218</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1190</v>
+        <v>1218</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1231</v>
+        <v>1249</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1231</v>
+        <v>1249</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1249</v>
+        <v>1272</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1249</v>
+        <v>1272</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1272</v>
+        <v>1292</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1272</v>
+        <v>1292</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1292</v>
+        <v>1316</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1292</v>
+        <v>1316</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1324</v>
+        <v>1359</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1324</v>
+        <v>1359</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1359</v>
+        <v>1377</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1359</v>
+        <v>1377</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1377</v>
+        <v>1399</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1377</v>
+        <v>1399</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1399</v>
+        <v>1415</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1399</v>
+        <v>1415</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>338</v>
+        <v>585</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1415</v>
+        <v>1434</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>338</v>
+        <v>585</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1415</v>
+        <v>1434</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>585</v>
+        <v>643</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1434</v>
+        <v>1452</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>585</v>
+        <v>643</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1434</v>
+        <v>1452</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1452</v>
+        <v>1476</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1452</v>
+        <v>1476</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -707,7 +707,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1491</v>
+        <v>1514</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -639,6 +639,47 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>南宁·布谷鸟动漫展4th</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>亭洪路45号 百益上河城</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024.06.09 10:00-06.10 17:00</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82241</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/uzZqZov91709281147333.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -969,7 +1010,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1491</v>
+        <v>1514</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1092,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1064,6 +1105,47 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202402/3syliqwc1706852024845.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>南宁·布谷鸟动漫展4th</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>亭洪路45号 百益上河城</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024.06.09 10:00-06.10 17:00</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82241</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/uzZqZov91709281147333.jpeg</t>
         </is>
       </c>
     </row>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1514</v>
+        <v>1534</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1514</v>
+        <v>1534</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>663</v>
+        <v>846</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1534</v>
+        <v>1570</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>663</v>
+        <v>846</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1534</v>
+        <v>1570</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>846</v>
+        <v>1071</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1570</v>
+        <v>1590</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>846</v>
+        <v>1071</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1570</v>
+        <v>1590</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1590</v>
+        <v>1625</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1590</v>
+        <v>1625</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>

--- a/南宁-漫展信息.xlsx
+++ b/南宁-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1625</v>
+        <v>1646</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1625</v>
+        <v>1646</v>
       </c>
       <c r="G4" t="n">
         <v>57</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>
